--- a/human_resources_surveys/011_hr_service_quality_survey--human_resources_surveys.xlsx
+++ b/human_resources_surveys/011_hr_service_quality_survey--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_1</t>
+          <t>employee_survey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>employee_survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Do you feel that the HR department has provided good quality services?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select all that apply</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Which department did you interact with recently?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select only one</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_2</t>
+          <t>comments_and_suggestions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>comments_and_suggestions</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Comments and suggestions for improvement?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide any comments or suggestions</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,18 +601,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>overall_satisfaction</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How would you rate your overall satisfaction with the HR service?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rate from 1 to 5</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_3</t>
+          <t>rating_comments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rating_comments</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Do you have any comments about your rating?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide any comments about your rating</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,25 +655,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_4</t>
+          <t>satisfaction_across_departments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>satisfaction_across_departments</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Are you satisfied with the services provided by the HR department across all departments?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,10 +687,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>next_steps</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What are the next steps for the HR department to improve services?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide any suggestions</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_5</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>comments_and_feedback</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Have you had any contact with the HR department recently?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>If yes, please provide email address</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_6</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is your phone number?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is your name?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide your name</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,61 +790,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_7</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your job title?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide your job title</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_8</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>job_title</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Which department do you work in?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select only one</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_9</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What date and time did you interact with the HR department?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_10</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What date did you interact with the HR department?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -837,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_11</t>
+          <t>time_taken</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>How long did you take to respond?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,228 +920,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_12</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Do you have any comments or feedback?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please provide any comments or feedback</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>hr_service_quality_survey_form_13</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>hr_service_quality_survey_form_14</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>hr_service_quality_survey_form_15</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>hr_service_quality_survey_form_15</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>rating_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>rating_2_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_2_comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>rating_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>rating_3_comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>hr_service_quality_survey_form_16</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>comments_2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,7 +958,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +983,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_1_choices</t>
+          <t>employee_survey_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1000,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_1_choices</t>
+          <t>employee_survey_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1165,12 +1022,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1182,114 +1039,114 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_4_choices</t>
+          <t>employee_survey_department_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_4_choices</t>
+          <t>satisfaction_across_departments_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>next_steps_choices</t>
+          <t>satisfaction_across_departments_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>next_steps_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_9_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hr_service_quality_survey_form_9_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
